--- a/data/trans_bre/P15B_3_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P15B_3_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,98</t>
+          <t>-8,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-76,59%</t>
+          <t>-76,24%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-51,47; -7,41</t>
+          <t>-54,8; -7,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 42,8</t>
+          <t>-12,3; 43,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 31,21</t>
+          <t>-10,95; 32,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 2,71</t>
+          <t>-34,58; 2,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-26,08%</t>
+          <t>-31,41%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,81; -2,94</t>
+          <t>-32,3; -2,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 5,1</t>
+          <t>-29,7; 6,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 9,12</t>
+          <t>-20,23; 8,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-20,88</t>
+          <t>-20,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-82,19%</t>
+          <t>-82,65%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-84,41; -48,39</t>
+          <t>-85,01; -50,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,6; -12,79</t>
+          <t>-34,95; -13,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-48,57; -13,98</t>
+          <t>-48,41; -15,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,17; -4,3</t>
+          <t>-37,47; -5,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,58</t>
+          <t>-100,0; 14,58</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-13,32</t>
+          <t>-12,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-49,18%</t>
+          <t>-48,51%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 22,47</t>
+          <t>-25,27; 22,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 0,09</t>
+          <t>-23,09; 3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 7,07</t>
+          <t>-19,24; 7,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 0,97</t>
+          <t>-25,1; 3,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,12; 112,19</t>
+          <t>-60,12; 102,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,8; 5,07</t>
+          <t>-78,58; 29,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 90,04</t>
+          <t>-82,98; 89,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,04; 17,44</t>
+          <t>-80,39; 21,0</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-28,38</t>
+          <t>-27,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-70,32%</t>
+          <t>-70,06%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 5,08</t>
+          <t>-55,24; 5,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-55,69; -21,5</t>
+          <t>-56,57; -21,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 11,61</t>
+          <t>-19,82; 12,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-49,21; -9,38</t>
+          <t>-50,1; -8,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 911426,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -62,77</t>
+          <t>-100,0; -61,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-82,44; 168,65</t>
+          <t>-80,0; 191,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-86,86; -36,36</t>
+          <t>-87,69; -30,88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-16,01</t>
+          <t>-15,45</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-67,82%</t>
+          <t>-67,77%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-33,22; -11,99</t>
+          <t>-33,02; -11,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -10,97</t>
+          <t>-22,25; -11,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,39</t>
+          <t>-13,35; -1,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,66; -9,51</t>
+          <t>-22,64; -8,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-85,6; -39,86</t>
+          <t>-86,24; -39,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-88,9; -56,79</t>
+          <t>-88,49; -56,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -9,8</t>
+          <t>-73,22; -6,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-81,45; -46,95</t>
+          <t>-80,37; -45,77</t>
         </is>
       </c>
     </row>
